--- a/source/Excel/Legacy_Excel.xlsx
+++ b/source/Excel/Legacy_Excel.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/ddd1d45b9ae2913d/Desktop/creditflow-data-warehouse/source/Excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="609" documentId="11_BB6BFAEF3CE56EECD85BAF3281E90443DD7C4B32" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DCE1F636-CFF2-4666-960D-39B82E6A8376}"/>
+  <xr:revisionPtr revIDLastSave="611" documentId="11_BB6BFAEF3CE56EECD85BAF3281E90443DD7C4B32" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E32C200C-3708-4221-93E1-29E5CD9F31A0}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Loan Book 2018-2019" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="4" r:id="rId11"/>
+    <pivotCache cacheId="0" r:id="rId11"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -53,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2633" uniqueCount="1225">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2633" uniqueCount="1226">
   <si>
     <t>Amount (PKR)</t>
   </si>
@@ -3728,6 +3728,9 @@
   </si>
   <si>
     <t>2023</t>
+  </si>
+  <si>
+    <t>Al Habib Textiles Pvt Ltd</t>
   </si>
 </sst>
 </file>
@@ -4236,176 +4239,6 @@
         <family val="2"/>
         <scheme val="none"/>
       </font>
-      <numFmt numFmtId="167" formatCode="#,##0.0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color rgb="FFFFFFFF"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF1F4E78"/>
-          <bgColor rgb="FF1F4E78"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="166" formatCode="[$-409]d\-mmm\-yyyy;@"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
       <numFmt numFmtId="3" formatCode="#,##0"/>
     </dxf>
     <dxf>
@@ -4693,6 +4526,176 @@
         </patternFill>
       </fill>
     </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="166" formatCode="[$-409]d\-mmm\-yyyy;@"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="167" formatCode="#,##0.0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF1F4E78"/>
+          <bgColor rgb="FF1F4E78"/>
+        </patternFill>
+      </fill>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -4704,6 +4707,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -4907,7 +4914,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{A9E1D02C-954F-443A-A5AB-FEAF43244388}" name="PivotTable1" cacheId="4" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{A9E1D02C-954F-443A-A5AB-FEAF43244388}" name="PivotTable1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A3:D17" firstHeaderRow="1" firstDataRow="5" firstDataCol="1"/>
   <pivotFields count="11">
     <pivotField axis="axisRow" showAll="0">
@@ -5052,51 +5059,51 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{A05BBCF6-1210-4DC0-9533-B5200DAA00DB}" name="LoanBook2018_2019" displayName="LoanBook2018_2019" ref="A1:H10" totalsRowShown="0" headerRowDxfId="44" dataDxfId="43">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{A05BBCF6-1210-4DC0-9533-B5200DAA00DB}" name="LoanBook2018_2019" displayName="LoanBook2018_2019" ref="A1:H10" totalsRowShown="0" headerRowDxfId="35" dataDxfId="34">
   <autoFilter ref="A1:H10" xr:uid="{A05BBCF6-1210-4DC0-9533-B5200DAA00DB}"/>
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{6F4F91A1-5EB1-45DE-A0B4-823805A3C26D}" name="Company " dataDxfId="42"/>
-    <tableColumn id="2" xr3:uid="{0EE21108-9482-497B-B8D7-8FB5F1856FC3}" name="Loan_Type" dataDxfId="41"/>
-    <tableColumn id="3" xr3:uid="{F771C2BD-7186-4D2D-9A03-D1F387C31B8F}" name="Amount (PKR)" dataDxfId="40" dataCellStyle="Comma"/>
-    <tableColumn id="7" xr3:uid="{337C5E84-FD05-462F-870C-6CBFE09F976D}" name="Currency " dataDxfId="39"/>
-    <tableColumn id="4" xr3:uid="{2D8521EB-3F32-4DEE-A8D2-2BCC413D4A6A}" name="Date " dataDxfId="38"/>
-    <tableColumn id="5" xr3:uid="{B53ED3AC-975A-4BCB-BA90-CD5004EC954C}" name="Status " dataDxfId="37"/>
-    <tableColumn id="8" xr3:uid="{43999634-8CC3-4B7A-9FD5-F1868B40D4E9}" name="Notes " dataDxfId="36"/>
-    <tableColumn id="9" xr3:uid="{9463979B-50CD-4BFE-BECC-FB920026A7EC}" name="Source_Block" dataDxfId="35"/>
+    <tableColumn id="1" xr3:uid="{6F4F91A1-5EB1-45DE-A0B4-823805A3C26D}" name="Company " dataDxfId="33"/>
+    <tableColumn id="2" xr3:uid="{0EE21108-9482-497B-B8D7-8FB5F1856FC3}" name="Loan_Type" dataDxfId="32"/>
+    <tableColumn id="3" xr3:uid="{F771C2BD-7186-4D2D-9A03-D1F387C31B8F}" name="Amount (PKR)" dataDxfId="31" dataCellStyle="Comma"/>
+    <tableColumn id="7" xr3:uid="{337C5E84-FD05-462F-870C-6CBFE09F976D}" name="Currency " dataDxfId="30"/>
+    <tableColumn id="4" xr3:uid="{2D8521EB-3F32-4DEE-A8D2-2BCC413D4A6A}" name="Date " dataDxfId="29"/>
+    <tableColumn id="5" xr3:uid="{B53ED3AC-975A-4BCB-BA90-CD5004EC954C}" name="Status " dataDxfId="28"/>
+    <tableColumn id="8" xr3:uid="{43999634-8CC3-4B7A-9FD5-F1868B40D4E9}" name="Notes " dataDxfId="27"/>
+    <tableColumn id="9" xr3:uid="{9463979B-50CD-4BFE-BECC-FB920026A7EC}" name="Source_Block" dataDxfId="26"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight8" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{D3547EAB-DFED-4FDB-88D1-2FF31D216BEA}" name="LoanBook2020_2021" displayName="LoanBook2020_2021" ref="A1:H10" totalsRowShown="0" headerRowDxfId="34" dataDxfId="33">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{D3547EAB-DFED-4FDB-88D1-2FF31D216BEA}" name="LoanBook2020_2021" displayName="LoanBook2020_2021" ref="A1:H10" totalsRowShown="0" headerRowDxfId="25" dataDxfId="24">
   <autoFilter ref="A1:H10" xr:uid="{D3547EAB-DFED-4FDB-88D1-2FF31D216BEA}"/>
   <tableColumns count="8">
-    <tableColumn id="2" xr3:uid="{DDF43C0F-2C20-4ECB-B696-D8C254759644}" name="Company " dataDxfId="32"/>
-    <tableColumn id="3" xr3:uid="{02B472B1-A7A7-40A0-8D6C-3238854C6FCD}" name="Loan_Type " dataDxfId="31"/>
-    <tableColumn id="4" xr3:uid="{DF82B8DF-AA80-439B-8924-A5B778451BEE}" name="Amount (PKR)" dataDxfId="30"/>
-    <tableColumn id="9" xr3:uid="{24417B60-B7A2-4BF6-A03B-93CDDCD232FF}" name="Currency " dataDxfId="29"/>
-    <tableColumn id="8" xr3:uid="{6886E7D0-E9AB-47E9-8BD6-5BE7CFB8376B}" name="Date" dataDxfId="28"/>
-    <tableColumn id="5" xr3:uid="{FE2227F6-EFD3-4D69-B2DE-078905CE4DD8}" name="Status " dataDxfId="27"/>
-    <tableColumn id="6" xr3:uid="{848C9ED1-F93B-432C-A481-114FA354AC15}" name="Notes " dataDxfId="26"/>
-    <tableColumn id="10" xr3:uid="{63B72437-E05B-4B81-A728-701FE83F532D}" name="Source_Block" dataDxfId="25"/>
+    <tableColumn id="2" xr3:uid="{DDF43C0F-2C20-4ECB-B696-D8C254759644}" name="Company " dataDxfId="23"/>
+    <tableColumn id="3" xr3:uid="{02B472B1-A7A7-40A0-8D6C-3238854C6FCD}" name="Loan_Type " dataDxfId="22"/>
+    <tableColumn id="4" xr3:uid="{DF82B8DF-AA80-439B-8924-A5B778451BEE}" name="Amount (PKR)" dataDxfId="21"/>
+    <tableColumn id="9" xr3:uid="{24417B60-B7A2-4BF6-A03B-93CDDCD232FF}" name="Currency " dataDxfId="20"/>
+    <tableColumn id="8" xr3:uid="{6886E7D0-E9AB-47E9-8BD6-5BE7CFB8376B}" name="Date" dataDxfId="19"/>
+    <tableColumn id="5" xr3:uid="{FE2227F6-EFD3-4D69-B2DE-078905CE4DD8}" name="Status " dataDxfId="18"/>
+    <tableColumn id="6" xr3:uid="{848C9ED1-F93B-432C-A481-114FA354AC15}" name="Notes " dataDxfId="17"/>
+    <tableColumn id="10" xr3:uid="{63B72437-E05B-4B81-A728-701FE83F532D}" name="Source_Block" dataDxfId="16"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight8" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{48AAD93C-FDAD-4126-8C35-A7F9362A6487}" name="LoanBook2022_2023" displayName="LoanBook2022_2023" ref="A1:H10" totalsRowShown="0" headerRowDxfId="24" dataDxfId="23">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{48AAD93C-FDAD-4126-8C35-A7F9362A6487}" name="LoanBook2022_2023" displayName="LoanBook2022_2023" ref="A1:H10" totalsRowShown="0" headerRowDxfId="44" dataDxfId="43">
   <autoFilter ref="A1:H10" xr:uid="{48AAD93C-FDAD-4126-8C35-A7F9362A6487}"/>
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{AEF07859-0BBA-41BC-8AA2-9EF1BF9FA0C5}" name="Company " dataDxfId="22"/>
-    <tableColumn id="2" xr3:uid="{A32039D9-A041-47C0-AFCA-BBCCBA9E4D68}" name="Loan_Type " dataDxfId="21"/>
-    <tableColumn id="4" xr3:uid="{57EB1DFC-1C60-4448-AE9C-3CC21FDA9E3D}" name="Amount (PKR)" dataDxfId="20"/>
+    <tableColumn id="1" xr3:uid="{AEF07859-0BBA-41BC-8AA2-9EF1BF9FA0C5}" name="Company " dataDxfId="42"/>
+    <tableColumn id="2" xr3:uid="{A32039D9-A041-47C0-AFCA-BBCCBA9E4D68}" name="Loan_Type " dataDxfId="41"/>
+    <tableColumn id="4" xr3:uid="{57EB1DFC-1C60-4448-AE9C-3CC21FDA9E3D}" name="Amount (PKR)" dataDxfId="40"/>
     <tableColumn id="5" xr3:uid="{2E47973A-F790-4CC7-8B43-E6D976DB957A}" name="Currency "/>
-    <tableColumn id="7" xr3:uid="{0D9B54D3-BF64-4D11-AC32-AD656FCA37E6}" name="Date" dataDxfId="19"/>
-    <tableColumn id="6" xr3:uid="{7D8DEAF7-265A-4939-85A4-C102A9FA1AA2}" name="Status " dataDxfId="18"/>
-    <tableColumn id="8" xr3:uid="{70D7F3A1-6863-4AAF-81AA-926E7A9D75F2}" name="Notes " dataDxfId="17"/>
-    <tableColumn id="9" xr3:uid="{3868B4B9-DAA8-4275-89CD-7ADE7182F836}" name="Source_Block" dataDxfId="16"/>
+    <tableColumn id="7" xr3:uid="{0D9B54D3-BF64-4D11-AC32-AD656FCA37E6}" name="Date" dataDxfId="39"/>
+    <tableColumn id="6" xr3:uid="{7D8DEAF7-265A-4939-85A4-C102A9FA1AA2}" name="Status " dataDxfId="38"/>
+    <tableColumn id="8" xr3:uid="{70D7F3A1-6863-4AAF-81AA-926E7A9D75F2}" name="Notes " dataDxfId="37"/>
+    <tableColumn id="9" xr3:uid="{3868B4B9-DAA8-4275-89CD-7ADE7182F836}" name="Source_Block" dataDxfId="36"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight8" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -5510,7 +5517,7 @@
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>6</v>
+        <v>1225</v>
       </c>
       <c r="B4" s="4" t="s">
         <v>7</v>
@@ -9317,7 +9324,7 @@
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>6</v>
+        <v>1225</v>
       </c>
       <c r="B9" s="4" t="s">
         <v>16</v>
